--- a/문서/Monster/MonsterAttackData.xlsx
+++ b/문서/Monster/MonsterAttackData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="Polaris Office Sheet" lastEdited="4" lowestEdited="4" rupBuild="10.105.307.56236"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="540" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="530" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,8 +23,15 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors/>
+  <commentList/>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t>idx</t>
   </si>
@@ -144,6 +151,60 @@
   </si>
   <si>
     <t>MonsterFallen</t>
+  </si>
+  <si>
+    <t>attackList</t>
+  </si>
+  <si>
+    <t>attackPreparation</t>
+  </si>
+  <si>
+    <t>attackRecovery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attackRange : </t>
+  </si>
+  <si>
+    <t>{[attackRange : ]}</t>
+  </si>
+  <si>
+    <t>{[attackRange : , attackPreparation:, ]}</t>
+  </si>
+  <si>
+    <t>{[attackRange : , attackPreparation:,attackRecovery: ]}</t>
+  </si>
+  <si>
+    <t>attackId</t>
+  </si>
+  <si>
+    <t>weight</t>
+  </si>
+  <si>
+    <t>triggerRange</t>
+  </si>
+  <si>
+    <t>damage</t>
+  </si>
+  <si>
+    <t>cooldown</t>
+  </si>
+  <si>
+    <t>attack</t>
+  </si>
+  <si>
+    <t>"Attack"</t>
+  </si>
+  <si>
+    <t>Attack</t>
+  </si>
+  <si>
+    <t>RollingAttack</t>
+  </si>
+  <si>
+    <t>SunkenAttack</t>
+  </si>
+  <si>
+    <t>weightRate</t>
   </si>
 </sst>
 </file>
@@ -151,7 +212,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <sz val="11.0"/>
       <name val="맑은 고딕"/>
@@ -255,6 +316,11 @@
       <sz val="11.0"/>
       <name val="맑은 고딕"/>
       <color rgb="FF7F7F7F"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="Carlito"/>
+      <color rgb="FF000000"/>
     </font>
   </fonts>
   <fills count="33">
@@ -695,7 +761,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -704,6 +770,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1023,40 +1096,125 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultColWidth="15.62500000" defaultRowHeight="16.500000"/>
   <cols>
     <col min="1" max="9" style="1" width="15.63000011" customWidth="1" outlineLevel="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
+        <v>47</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>30001</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
+        <v>54</v>
+      </c>
+      <c r="C2" s="1">
+        <v>100</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1">
+        <v>10</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>30002</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>39</v>
+        <v>54</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1">
+        <v>10</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="1">
+        <v>30002</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="1">
+        <v>20</v>
+      </c>
+      <c r="D4" s="1">
+        <v>10</v>
+      </c>
+      <c r="E4" s="1">
+        <v>10</v>
+      </c>
+      <c r="F4" s="1">
+        <v>15</v>
+      </c>
+      <c r="G4" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="1">
+        <v>30002</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" s="1">
+        <v>80</v>
+      </c>
+      <c r="D5" s="1">
+        <v>5</v>
+      </c>
+      <c r="E5" s="1">
+        <v>5</v>
+      </c>
+      <c r="F5" s="1">
+        <v>15</v>
+      </c>
+      <c r="G5" s="1">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1069,12 +1227,29 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.500000"/>
-  <sheetData/>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultColWidth="15.62500000" defaultRowHeight="16.500000"/>
+  <cols>
+    <col min="1" max="16384" style="1" width="15.63000011" customWidth="1" outlineLevel="0"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="5"/>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.70" right="0.70" top="0.75" bottom="0.75" header="0.30" footer="0.30"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/문서/Monster/MonsterAttackData.xlsx
+++ b/문서/Monster/MonsterAttackData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="Polaris Office Sheet" lastEdited="4" lowestEdited="4" rupBuild="10.105.307.56236"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="530" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="520" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1102,7 +1102,7 @@
     <col min="1" max="9" style="1" width="15.63000011" customWidth="1" outlineLevel="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>36</v>
       </c>
@@ -1124,8 +1124,11 @@
       <c r="G1" s="1" t="s">
         <v>51</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>41</v>
+      </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>30001</v>
       </c>
@@ -1147,8 +1150,11 @@
       <c r="G2" s="1">
         <v>1</v>
       </c>
+      <c r="H2" s="1">
+        <v>0.5</v>
+      </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>30002</v>
       </c>
@@ -1170,8 +1176,11 @@
       <c r="G3" s="1">
         <v>1</v>
       </c>
+      <c r="H3" s="1">
+        <v>0.5</v>
+      </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>30002</v>
       </c>
@@ -1193,8 +1202,11 @@
       <c r="G4" s="1">
         <v>3</v>
       </c>
+      <c r="H4" s="1">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>30002</v>
       </c>
@@ -1215,6 +1227,9 @@
       </c>
       <c r="G5" s="1">
         <v>2</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
